--- a/research/traditional_assets/database/data/argentina/argentina_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_telecom_services.xlsx
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.585</v>
+        <v>0.5670000000000001</v>
       </c>
       <c r="G2">
-        <v>0.4007411894665573</v>
+        <v>0.5084863604760541</v>
       </c>
       <c r="H2">
-        <v>0.4007411894665573</v>
+        <v>0.5084863604760541</v>
       </c>
       <c r="I2">
-        <v>-0.02622670420126144</v>
+        <v>-0.0625741278475318</v>
       </c>
       <c r="J2">
-        <v>-0.01311335210063072</v>
+        <v>-0.0625741278475318</v>
       </c>
       <c r="K2">
-        <v>-28.9</v>
+        <v>-1064.8</v>
       </c>
       <c r="L2">
-        <v>-0.01029825749207141</v>
+        <v>-0.4354832113206004</v>
       </c>
       <c r="M2">
-        <v>1.21</v>
+        <v>2.63</v>
       </c>
       <c r="N2">
-        <v>0.0002853975517135647</v>
+        <v>0.0005901492202400987</v>
       </c>
       <c r="O2">
-        <v>-0.04186851211072665</v>
+        <v>-0.002469947407963937</v>
       </c>
       <c r="P2">
-        <v>1.21</v>
+        <v>2.63</v>
       </c>
       <c r="Q2">
-        <v>0.0002853975517135647</v>
+        <v>0.0005901492202400987</v>
       </c>
       <c r="R2">
-        <v>-0.04186851211072665</v>
+        <v>-0.002469947407963937</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +633,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>172.9</v>
+        <v>223.5</v>
       </c>
       <c r="V2">
-        <v>0.04078118734816143</v>
+        <v>0.05015146415348368</v>
       </c>
       <c r="W2">
-        <v>-0.005937827453719874</v>
+        <v>-0.2168547106024195</v>
       </c>
       <c r="X2">
-        <v>0.1502156748167047</v>
+        <v>0.2416943485095713</v>
       </c>
       <c r="Y2">
-        <v>-0.1561535022704246</v>
+        <v>-0.4585490591119908</v>
       </c>
       <c r="Z2">
-        <v>0.7012769572931503</v>
+        <v>0.6203003703891623</v>
       </c>
       <c r="AA2">
-        <v>-0.009196091661044055</v>
+        <v>-0.03881475468060277</v>
       </c>
       <c r="AB2">
-        <v>0.1449417947581376</v>
+        <v>0.2183557127439922</v>
       </c>
       <c r="AC2">
-        <v>-0.1541378864191817</v>
+        <v>-0.2571704674245949</v>
       </c>
       <c r="AD2">
-        <v>2694.8</v>
+        <v>2877.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2694.8</v>
+        <v>2877.7</v>
       </c>
       <c r="AG2">
-        <v>2521.9</v>
+        <v>2654.2</v>
       </c>
       <c r="AH2">
-        <v>0.3886076862066479</v>
+        <v>0.3923672656867824</v>
       </c>
       <c r="AI2">
-        <v>0.3507347103458149</v>
+        <v>0.3758800402304106</v>
       </c>
       <c r="AJ2">
-        <v>0.3729738523426408</v>
+        <v>0.3732684545825306</v>
       </c>
       <c r="AK2">
-        <v>0.3357877077119727</v>
+        <v>0.3571121037619073</v>
       </c>
       <c r="AL2">
-        <v>109.9</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>109.9</v>
+        <v>-8.85</v>
       </c>
       <c r="AN2">
-        <v>3.52537938252224</v>
-      </c>
-      <c r="AO2">
-        <v>-0.6696997270245677</v>
+        <v>4.851964255606137</v>
       </c>
       <c r="AP2">
-        <v>3.299188906331764</v>
+        <v>4.475130669364356</v>
       </c>
       <c r="AQ2">
-        <v>-0.6696997270245677</v>
+        <v>17.28813559322034</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +716,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.585</v>
+        <v>0.5670000000000001</v>
       </c>
       <c r="G3">
-        <v>0.4007411894665573</v>
+        <v>0.5084863604760541</v>
       </c>
       <c r="H3">
-        <v>0.4007411894665573</v>
+        <v>0.5084863604760541</v>
       </c>
       <c r="I3">
-        <v>-0.02622670420126144</v>
+        <v>-0.0625741278475318</v>
       </c>
       <c r="J3">
-        <v>-0.01311335210063072</v>
+        <v>-0.0625741278475318</v>
       </c>
       <c r="K3">
-        <v>-28.9</v>
+        <v>-1064.8</v>
       </c>
       <c r="L3">
-        <v>-0.01029825749207141</v>
+        <v>-0.4354832113206004</v>
       </c>
       <c r="M3">
-        <v>1.21</v>
+        <v>2.63</v>
       </c>
       <c r="N3">
-        <v>0.0002853975517135647</v>
+        <v>0.0005901492202400987</v>
       </c>
       <c r="O3">
-        <v>-0.04186851211072665</v>
+        <v>-0.002469947407963937</v>
       </c>
       <c r="P3">
-        <v>1.21</v>
+        <v>2.63</v>
       </c>
       <c r="Q3">
-        <v>0.0002853975517135647</v>
+        <v>0.0005901492202400987</v>
       </c>
       <c r="R3">
-        <v>-0.04186851211072665</v>
+        <v>-0.002469947407963937</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +761,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>172.9</v>
+        <v>223.5</v>
       </c>
       <c r="V3">
-        <v>0.04078118734816143</v>
+        <v>0.05015146415348368</v>
       </c>
       <c r="W3">
-        <v>-0.005937827453719874</v>
+        <v>-0.2168547106024195</v>
       </c>
       <c r="X3">
-        <v>0.1502156748167047</v>
+        <v>0.2416943485095713</v>
       </c>
       <c r="Y3">
-        <v>-0.1561535022704246</v>
+        <v>-0.4585490591119908</v>
       </c>
       <c r="Z3">
-        <v>0.7012769572931503</v>
+        <v>0.6203003703891623</v>
       </c>
       <c r="AA3">
-        <v>-0.009196091661044055</v>
+        <v>-0.03881475468060277</v>
       </c>
       <c r="AB3">
-        <v>0.1449417947581376</v>
+        <v>0.2183557127439922</v>
       </c>
       <c r="AC3">
-        <v>-0.1541378864191817</v>
+        <v>-0.2571704674245949</v>
       </c>
       <c r="AD3">
-        <v>2694.8</v>
+        <v>2877.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2694.8</v>
+        <v>2877.7</v>
       </c>
       <c r="AG3">
-        <v>2521.9</v>
+        <v>2654.2</v>
       </c>
       <c r="AH3">
-        <v>0.3886076862066479</v>
+        <v>0.3923672656867824</v>
       </c>
       <c r="AI3">
-        <v>0.3507347103458149</v>
+        <v>0.3758800402304106</v>
       </c>
       <c r="AJ3">
-        <v>0.3729738523426408</v>
+        <v>0.3732684545825306</v>
       </c>
       <c r="AK3">
-        <v>0.3357877077119727</v>
+        <v>0.3571121037619073</v>
       </c>
       <c r="AL3">
-        <v>109.9</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>109.9</v>
+        <v>-8.85</v>
       </c>
       <c r="AN3">
-        <v>3.52537938252224</v>
-      </c>
-      <c r="AO3">
-        <v>-0.6696997270245677</v>
+        <v>4.851964255606137</v>
       </c>
       <c r="AP3">
-        <v>3.299188906331764</v>
+        <v>4.475130669364356</v>
       </c>
       <c r="AQ3">
-        <v>-0.6696997270245677</v>
+        <v>17.28813559322034</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_telecom_services.xlsx
@@ -588,115 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.5670000000000001</v>
+        <v>0.243</v>
       </c>
       <c r="G2">
-        <v>0.5084863604760541</v>
+        <v>0.5392425905598244</v>
       </c>
       <c r="H2">
-        <v>0.5084863604760541</v>
+        <v>0.5392425905598244</v>
       </c>
       <c r="I2">
-        <v>-0.0625741278475318</v>
+        <v>-0.06959385290889132</v>
       </c>
       <c r="J2">
-        <v>-0.0625741278475318</v>
+        <v>-0.06959385290889132</v>
       </c>
       <c r="K2">
-        <v>-1064.8</v>
+        <v>760.9</v>
       </c>
       <c r="L2">
-        <v>-0.4354832113206004</v>
+        <v>0.4176180021953897</v>
       </c>
       <c r="M2">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0005901492202400987</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.002469947407963937</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0005901492202400987</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.002469947407963937</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>223.5</v>
+        <v>280.5</v>
       </c>
       <c r="V2">
-        <v>0.05015146415348368</v>
+        <v>0.07612973266386212</v>
       </c>
       <c r="W2">
-        <v>-0.2168547106024195</v>
+        <v>0.1622457247643823</v>
       </c>
       <c r="X2">
-        <v>0.2416943485095713</v>
+        <v>0.214944861001981</v>
       </c>
       <c r="Y2">
-        <v>-0.4585490591119908</v>
+        <v>-0.0526991362375987</v>
       </c>
       <c r="Z2">
-        <v>0.6203003703891623</v>
+        <v>0.4068780705672175</v>
       </c>
       <c r="AA2">
-        <v>-0.03881475468060277</v>
+        <v>-0.02831621259490844</v>
       </c>
       <c r="AB2">
-        <v>0.2183557127439922</v>
+        <v>0.1982126316357257</v>
       </c>
       <c r="AC2">
-        <v>-0.2571704674245949</v>
+        <v>-0.2265288442306341</v>
       </c>
       <c r="AD2">
-        <v>2877.7</v>
+        <v>2792.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2877.7</v>
+        <v>2792.8</v>
       </c>
       <c r="AG2">
-        <v>2654.2</v>
+        <v>2512.3</v>
       </c>
       <c r="AH2">
-        <v>0.3923672656867824</v>
+        <v>0.4311673073657234</v>
       </c>
       <c r="AI2">
-        <v>0.3758800402304106</v>
+        <v>0.3700494229571624</v>
       </c>
       <c r="AJ2">
-        <v>0.3732684545825306</v>
+        <v>0.4054189258972373</v>
       </c>
       <c r="AK2">
-        <v>0.3571121037619073</v>
+        <v>0.3457325296562354</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="AM2">
-        <v>-8.85</v>
+        <v>50.8</v>
       </c>
       <c r="AN2">
-        <v>4.851964255606137</v>
+        <v>6.785228377065112</v>
+      </c>
+      <c r="AO2">
+        <v>-2.0288</v>
       </c>
       <c r="AP2">
-        <v>4.475130669364356</v>
+        <v>6.10374149659864</v>
       </c>
       <c r="AQ2">
-        <v>17.28813559322034</v>
+        <v>-2.496062992125984</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.5670000000000001</v>
+        <v>0.243</v>
       </c>
       <c r="G3">
-        <v>0.5084863604760541</v>
+        <v>0.5392425905598244</v>
       </c>
       <c r="H3">
-        <v>0.5084863604760541</v>
+        <v>0.5392425905598244</v>
       </c>
       <c r="I3">
-        <v>-0.0625741278475318</v>
+        <v>-0.06959385290889132</v>
       </c>
       <c r="J3">
-        <v>-0.0625741278475318</v>
+        <v>-0.06959385290889132</v>
       </c>
       <c r="K3">
-        <v>-1064.8</v>
+        <v>760.9</v>
       </c>
       <c r="L3">
-        <v>-0.4354832113206004</v>
+        <v>0.4176180021953897</v>
       </c>
       <c r="M3">
-        <v>2.63</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0005901492202400987</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.002469947407963937</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>2.63</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0005901492202400987</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.002469947407963937</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>223.5</v>
+        <v>280.5</v>
       </c>
       <c r="V3">
-        <v>0.05015146415348368</v>
+        <v>0.07612973266386212</v>
       </c>
       <c r="W3">
-        <v>-0.2168547106024195</v>
+        <v>0.1622457247643823</v>
       </c>
       <c r="X3">
-        <v>0.2416943485095713</v>
+        <v>0.214944861001981</v>
       </c>
       <c r="Y3">
-        <v>-0.4585490591119908</v>
+        <v>-0.0526991362375987</v>
       </c>
       <c r="Z3">
-        <v>0.6203003703891623</v>
+        <v>0.4068780705672175</v>
       </c>
       <c r="AA3">
-        <v>-0.03881475468060277</v>
+        <v>-0.02831621259490844</v>
       </c>
       <c r="AB3">
-        <v>0.2183557127439922</v>
+        <v>0.1982126316357257</v>
       </c>
       <c r="AC3">
-        <v>-0.2571704674245949</v>
+        <v>-0.2265288442306341</v>
       </c>
       <c r="AD3">
-        <v>2877.7</v>
+        <v>2792.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2877.7</v>
+        <v>2792.8</v>
       </c>
       <c r="AG3">
-        <v>2654.2</v>
+        <v>2512.3</v>
       </c>
       <c r="AH3">
-        <v>0.3923672656867824</v>
+        <v>0.4311673073657234</v>
       </c>
       <c r="AI3">
-        <v>0.3758800402304106</v>
+        <v>0.3700494229571624</v>
       </c>
       <c r="AJ3">
-        <v>0.3732684545825306</v>
+        <v>0.4054189258972373</v>
       </c>
       <c r="AK3">
-        <v>0.3571121037619073</v>
+        <v>0.3457325296562354</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="AM3">
-        <v>-8.85</v>
+        <v>50.8</v>
       </c>
       <c r="AN3">
-        <v>4.851964255606137</v>
+        <v>6.785228377065112</v>
+      </c>
+      <c r="AO3">
+        <v>-2.0288</v>
       </c>
       <c r="AP3">
-        <v>4.475130669364356</v>
+        <v>6.10374149659864</v>
       </c>
       <c r="AQ3">
-        <v>17.28813559322034</v>
+        <v>-2.496062992125984</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_telecom_services.xlsx
@@ -588,115 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.243</v>
+        <v>0.42</v>
+      </c>
+      <c r="E2">
+        <v>1.866</v>
       </c>
       <c r="G2">
-        <v>0.5392425905598244</v>
+        <v>0.3603168361328015</v>
       </c>
       <c r="H2">
-        <v>0.5392425905598244</v>
+        <v>0.3603168361328015</v>
       </c>
       <c r="I2">
-        <v>-0.06959385290889132</v>
+        <v>-0.04527835514858716</v>
       </c>
       <c r="J2">
-        <v>-0.06959385290889132</v>
+        <v>-0.02624857392209682</v>
       </c>
       <c r="K2">
-        <v>760.9</v>
+        <v>443.1</v>
       </c>
       <c r="L2">
-        <v>0.4176180021953897</v>
+        <v>0.2489186000786473</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0006470725812738754</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.009365831640713158</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0006470725812738754</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.009365831640713158</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>280.5</v>
+        <v>188.5</v>
       </c>
       <c r="V2">
-        <v>0.07612973266386212</v>
+        <v>0.02939112808918687</v>
       </c>
       <c r="W2">
-        <v>0.1622457247643823</v>
+        <v>0.09515730699022872</v>
       </c>
       <c r="X2">
-        <v>0.214944861001981</v>
+        <v>0.1866730717472016</v>
       </c>
       <c r="Y2">
-        <v>-0.0526991362375987</v>
+        <v>-0.09151576475697291</v>
       </c>
       <c r="Z2">
-        <v>0.4068780705672175</v>
+        <v>0.414285049339043</v>
       </c>
       <c r="AA2">
-        <v>-0.02831621259490844</v>
+        <v>-0.0108743917423954</v>
       </c>
       <c r="AB2">
-        <v>0.1982126316357257</v>
+        <v>0.176473728875713</v>
       </c>
       <c r="AC2">
-        <v>-0.2265288442306341</v>
+        <v>-0.1873481206181084</v>
       </c>
       <c r="AD2">
-        <v>2792.8</v>
+        <v>2955.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2792.8</v>
+        <v>2955.6</v>
       </c>
       <c r="AG2">
-        <v>2512.3</v>
+        <v>2767.1</v>
       </c>
       <c r="AH2">
-        <v>0.4311673073657234</v>
+        <v>0.3154625310862302</v>
       </c>
       <c r="AI2">
-        <v>0.3700494229571624</v>
+        <v>0.3537056760929141</v>
       </c>
       <c r="AJ2">
-        <v>0.4054189258972373</v>
+        <v>0.301407315426007</v>
       </c>
       <c r="AK2">
-        <v>0.3457325296562354</v>
+        <v>0.3387898525882756</v>
       </c>
       <c r="AL2">
-        <v>62.5</v>
+        <v>56.9</v>
       </c>
       <c r="AM2">
-        <v>50.8</v>
+        <v>45.8</v>
       </c>
       <c r="AN2">
-        <v>6.785228377065112</v>
+        <v>7.885805763073638</v>
       </c>
       <c r="AO2">
-        <v>-2.0288</v>
+        <v>-1.416520210896309</v>
       </c>
       <c r="AP2">
-        <v>6.10374149659864</v>
+        <v>7.382870864461045</v>
       </c>
       <c r="AQ2">
-        <v>-2.496062992125984</v>
+        <v>-1.759825327510917</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.243</v>
+        <v>0.42</v>
+      </c>
+      <c r="E3">
+        <v>1.866</v>
       </c>
       <c r="G3">
-        <v>0.5392425905598244</v>
+        <v>0.3603168361328015</v>
       </c>
       <c r="H3">
-        <v>0.5392425905598244</v>
+        <v>0.3603168361328015</v>
       </c>
       <c r="I3">
-        <v>-0.06959385290889132</v>
+        <v>-0.04527835514858716</v>
       </c>
       <c r="J3">
-        <v>-0.06959385290889132</v>
+        <v>-0.02624857392209682</v>
       </c>
       <c r="K3">
-        <v>760.9</v>
+        <v>443.1</v>
       </c>
       <c r="L3">
-        <v>0.4176180021953897</v>
+        <v>0.2489186000786473</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>4.15</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0006470725812738754</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.009365831640713158</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>4.15</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0006470725812738754</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.009365831640713158</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>280.5</v>
+        <v>188.5</v>
       </c>
       <c r="V3">
-        <v>0.07612973266386212</v>
+        <v>0.02939112808918687</v>
       </c>
       <c r="W3">
-        <v>0.1622457247643823</v>
+        <v>0.09515730699022872</v>
       </c>
       <c r="X3">
-        <v>0.214944861001981</v>
+        <v>0.1866730717472016</v>
       </c>
       <c r="Y3">
-        <v>-0.0526991362375987</v>
+        <v>-0.09151576475697291</v>
       </c>
       <c r="Z3">
-        <v>0.4068780705672175</v>
+        <v>0.414285049339043</v>
       </c>
       <c r="AA3">
-        <v>-0.02831621259490844</v>
+        <v>-0.0108743917423954</v>
       </c>
       <c r="AB3">
-        <v>0.1982126316357257</v>
+        <v>0.176473728875713</v>
       </c>
       <c r="AC3">
-        <v>-0.2265288442306341</v>
+        <v>-0.1873481206181084</v>
       </c>
       <c r="AD3">
-        <v>2792.8</v>
+        <v>2955.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2792.8</v>
+        <v>2955.6</v>
       </c>
       <c r="AG3">
-        <v>2512.3</v>
+        <v>2767.1</v>
       </c>
       <c r="AH3">
-        <v>0.4311673073657234</v>
+        <v>0.3154625310862302</v>
       </c>
       <c r="AI3">
-        <v>0.3700494229571624</v>
+        <v>0.3537056760929141</v>
       </c>
       <c r="AJ3">
-        <v>0.4054189258972373</v>
+        <v>0.301407315426007</v>
       </c>
       <c r="AK3">
-        <v>0.3457325296562354</v>
+        <v>0.3387898525882756</v>
       </c>
       <c r="AL3">
-        <v>62.5</v>
+        <v>56.9</v>
       </c>
       <c r="AM3">
-        <v>50.8</v>
+        <v>45.8</v>
       </c>
       <c r="AN3">
-        <v>6.785228377065112</v>
+        <v>7.885805763073638</v>
       </c>
       <c r="AO3">
-        <v>-2.0288</v>
+        <v>-1.416520210896309</v>
       </c>
       <c r="AP3">
-        <v>6.10374149659864</v>
+        <v>7.382870864461045</v>
       </c>
       <c r="AQ3">
-        <v>-2.496062992125984</v>
+        <v>-1.759825327510917</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_telecom_services.xlsx
@@ -645,10 +645,10 @@
         <v>0.09515730699022872</v>
       </c>
       <c r="X2">
-        <v>0.1866730717472016</v>
+        <v>0.1867076405975019</v>
       </c>
       <c r="Y2">
-        <v>-0.09151576475697291</v>
+        <v>-0.09155033360727317</v>
       </c>
       <c r="Z2">
         <v>0.414285049339043</v>
@@ -657,10 +657,10 @@
         <v>-0.0108743917423954</v>
       </c>
       <c r="AB2">
-        <v>0.176473728875713</v>
+        <v>0.1764973925490008</v>
       </c>
       <c r="AC2">
-        <v>-0.1873481206181084</v>
+        <v>-0.1873717842913962</v>
       </c>
       <c r="AD2">
         <v>2955.6</v>
@@ -779,10 +779,10 @@
         <v>0.09515730699022872</v>
       </c>
       <c r="X3">
-        <v>0.1866730717472016</v>
+        <v>0.1867076405975019</v>
       </c>
       <c r="Y3">
-        <v>-0.09151576475697291</v>
+        <v>-0.09155033360727317</v>
       </c>
       <c r="Z3">
         <v>0.414285049339043</v>
@@ -791,10 +791,10 @@
         <v>-0.0108743917423954</v>
       </c>
       <c r="AB3">
-        <v>0.176473728875713</v>
+        <v>0.1764973925490008</v>
       </c>
       <c r="AC3">
-        <v>-0.1873481206181084</v>
+        <v>-0.1873717842913962</v>
       </c>
       <c r="AD3">
         <v>2955.6</v>
